--- a/解题-gpt/结果/问题四_3批次_修复版.xlsx
+++ b/解题-gpt/结果/问题四_3批次_修复版.xlsx
@@ -542,34 +542,34 @@
         <v>2100</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>132.0721581834358</v>
+        <v>103.1152421386595</v>
       </c>
       <c r="G2" t="n">
-        <v>8.375285829114478</v>
+        <v>7.562048201282888</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -603,16 +603,16 @@
         <v>1171</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>205.6147938843214</v>
+        <v>171.5840041697735</v>
       </c>
       <c r="G3" t="n">
-        <v>91.2075882433958</v>
+        <v>80.35225252017339</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -627,19 +627,19 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
@@ -668,16 +668,16 @@
         <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>175.5971140574344</v>
+        <v>135.5260548356059</v>
       </c>
       <c r="G4" t="n">
-        <v>6.699789184287249</v>
+        <v>5.93966133591477</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -689,13 +689,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -854,7 +854,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
         <v>2</v>
@@ -863,13 +863,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
